--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95429A6B-571B-483A-A2EE-B27AD16AD00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24CEE40-7404-4AFB-B968-1781631DEA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="COPD" sheetId="13" r:id="rId3"/>
     <sheet name="Recruitment" sheetId="14" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="184">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -774,6 +774,21 @@
   </si>
   <si>
     <t>{v} &lt; 1</t>
+  </si>
+  <si>
+    <t>{v} = 18</t>
+  </si>
+  <si>
+    <t>{v} = 60</t>
+  </si>
+  <si>
+    <t>{v} = 0.37</t>
+  </si>
+  <si>
+    <t>{v} = 0.12</t>
+  </si>
+  <si>
+    <t>{v} = 438</t>
   </si>
 </sst>
 </file>
@@ -1021,16 +1036,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1042,14 +1051,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1069,8 +1075,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1470,50 +1485,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="177.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1525,13 +1540,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="16" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1548,74 +1563,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="18"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="27"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="26"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="31"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1627,13 +1642,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1643,13 +1658,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
     </row>
@@ -1657,13 +1672,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="9" t="s">
         <v>105</v>
       </c>
@@ -1673,13 +1688,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1729,7 +1744,7 @@
       <c r="G16" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
@@ -1751,7 +1766,7 @@
       <c r="G17" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
@@ -1773,7 +1788,7 @@
       <c r="G18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
@@ -1795,7 +1810,7 @@
       <c r="G19" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
@@ -1817,7 +1832,7 @@
       <c r="G20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
@@ -1839,7 +1854,7 @@
       <c r="G21" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
@@ -1861,7 +1876,7 @@
       <c r="G22" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
@@ -1883,7 +1898,7 @@
       <c r="G23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H23" s="32"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
@@ -1905,7 +1920,7 @@
       <c r="G24" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="32"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
@@ -1927,7 +1942,7 @@
       <c r="G25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
@@ -1949,7 +1964,7 @@
       <c r="G26" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H26" s="32"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -1971,30 +1986,30 @@
       <c r="G27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2024,50 +2039,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="241.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2079,13 +2094,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="16" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2102,74 +2117,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="18"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="27"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="26"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="31"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2181,13 +2196,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -2195,13 +2210,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="9" t="s">
         <v>57</v>
       </c>
@@ -2211,13 +2226,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -2227,13 +2242,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -2241,13 +2256,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
         <v>106</v>
       </c>
@@ -2257,13 +2272,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -2313,7 +2328,7 @@
       <c r="G18" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
@@ -2335,7 +2350,7 @@
       <c r="G19" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
@@ -2357,7 +2372,7 @@
       <c r="G20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
@@ -2379,7 +2394,7 @@
       <c r="G21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
@@ -2401,7 +2416,7 @@
       <c r="G22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
@@ -2423,7 +2438,7 @@
       <c r="G23" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H23" s="32"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
@@ -2445,7 +2460,7 @@
       <c r="G24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="32"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
@@ -2467,7 +2482,7 @@
       <c r="G25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
@@ -2489,7 +2504,7 @@
       <c r="G26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="32"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -2511,7 +2526,7 @@
       <c r="G27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
@@ -2533,7 +2548,7 @@
       <c r="G28" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="32"/>
+      <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
@@ -2555,19 +2570,19 @@
       <c r="G29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H29" s="32"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
@@ -2579,13 +2594,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
       <c r="G31" s="9" t="s">
         <v>56</v>
       </c>
@@ -2595,13 +2610,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
       <c r="G32" s="9" t="s">
         <v>107</v>
       </c>
@@ -2611,13 +2626,13 @@
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -2667,7 +2682,7 @@
       <c r="G35" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
@@ -2689,7 +2704,7 @@
       <c r="G36" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H36" s="32"/>
+      <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
@@ -2711,7 +2726,7 @@
       <c r="G37" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H37" s="32"/>
+      <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -2733,7 +2748,7 @@
       <c r="G38" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H38" s="32"/>
+      <c r="H38" s="16"/>
     </row>
     <row r="39" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
@@ -2755,7 +2770,7 @@
       <c r="G39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H39" s="32"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
@@ -2777,7 +2792,7 @@
       <c r="G40" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H40" s="32"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
@@ -2799,7 +2814,7 @@
       <c r="G41" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H41" s="32"/>
+      <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
@@ -2821,7 +2836,7 @@
       <c r="G42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H42" s="32"/>
+      <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
@@ -2843,7 +2858,7 @@
       <c r="G43" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H43" s="32"/>
+      <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
@@ -2865,7 +2880,7 @@
       <c r="G44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H44" s="32"/>
+      <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
@@ -2887,7 +2902,7 @@
       <c r="G45" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H45" s="32"/>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
@@ -2909,19 +2924,19 @@
       <c r="G46" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H46" s="32"/>
+      <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2933,13 +2948,13 @@
       <c r="A48" s="8">
         <v>3</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
       <c r="G48" s="9" t="s">
         <v>70</v>
       </c>
@@ -2949,13 +2964,13 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
       <c r="G49" s="9" t="s">
         <v>108</v>
       </c>
@@ -2965,13 +2980,13 @@
       <c r="A50" s="8">
         <v>3</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
@@ -3021,7 +3036,7 @@
       <c r="G52" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H52" s="32"/>
+      <c r="H52" s="16"/>
     </row>
     <row r="53" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
@@ -3043,7 +3058,7 @@
       <c r="G53" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H53" s="32"/>
+      <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
@@ -3065,7 +3080,7 @@
       <c r="G54" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H54" s="32"/>
+      <c r="H54" s="16"/>
     </row>
     <row r="55" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
@@ -3087,7 +3102,7 @@
       <c r="G55" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H55" s="32"/>
+      <c r="H55" s="16"/>
     </row>
     <row r="56" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
@@ -3109,7 +3124,7 @@
       <c r="G56" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H56" s="32"/>
+      <c r="H56" s="16"/>
     </row>
     <row r="57" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
@@ -3131,7 +3146,7 @@
       <c r="G57" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H57" s="32"/>
+      <c r="H57" s="16"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
@@ -3153,7 +3168,7 @@
       <c r="G58" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H58" s="32"/>
+      <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
@@ -3175,7 +3190,7 @@
       <c r="G59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H59" s="32"/>
+      <c r="H59" s="16"/>
     </row>
     <row r="60" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
@@ -3197,7 +3212,7 @@
       <c r="G60" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H60" s="32"/>
+      <c r="H60" s="16"/>
     </row>
     <row r="61" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
@@ -3219,7 +3234,7 @@
       <c r="G61" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H61" s="32"/>
+      <c r="H61" s="16"/>
     </row>
     <row r="62" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
@@ -3241,7 +3256,7 @@
       <c r="G62" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H62" s="32"/>
+      <c r="H62" s="16"/>
     </row>
     <row r="63" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
@@ -3263,20 +3278,19 @@
       <c r="G63" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H63" s="32"/>
+      <c r="H63" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -3288,15 +3302,16 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3325,50 +3340,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3380,13 +3395,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="16" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3403,74 +3418,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="18"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="27"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="26"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="31"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3482,13 +3497,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3496,13 +3511,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="9" t="s">
         <v>58</v>
       </c>
@@ -3512,13 +3527,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -3528,13 +3543,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3542,13 +3557,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
         <v>132</v>
       </c>
@@ -3558,13 +3573,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3604,8 +3619,8 @@
       <c r="C18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="2">
-        <v>12</v>
+      <c r="D18" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>83</v>
@@ -3614,7 +3629,7 @@
       <c r="G18" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
@@ -3626,8 +3641,8 @@
       <c r="C19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="2">
-        <v>18</v>
+      <c r="D19" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -3636,7 +3651,7 @@
       <c r="G19" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
@@ -3648,8 +3663,8 @@
       <c r="C20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="2">
-        <v>60</v>
+      <c r="D20" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>79</v>
@@ -3658,7 +3673,7 @@
       <c r="G20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
@@ -3670,8 +3685,8 @@
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="2">
-        <v>0.37</v>
+      <c r="D21" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>84</v>
@@ -3680,7 +3695,7 @@
       <c r="G21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
@@ -3692,8 +3707,8 @@
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="2">
-        <v>0.12</v>
+      <c r="D22" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>85</v>
@@ -3702,7 +3717,7 @@
       <c r="G22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
@@ -3714,8 +3729,8 @@
       <c r="C23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="2">
-        <v>438</v>
+      <c r="D23" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>79</v>
@@ -3724,7 +3739,7 @@
       <c r="G23" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H23" s="32"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
@@ -3746,7 +3761,7 @@
       <c r="G24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="32"/>
+      <c r="H24" s="16"/>
     </row>
     <row r="25" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
@@ -3768,7 +3783,7 @@
       <c r="G25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
@@ -3790,7 +3805,7 @@
       <c r="G26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="32"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -3812,19 +3827,19 @@
       <c r="G27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
@@ -3836,13 +3851,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
       <c r="G29" s="9" t="s">
         <v>71</v>
       </c>
@@ -3852,13 +3867,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="25"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
       <c r="G30" s="9" t="s">
         <v>109</v>
       </c>
@@ -3868,13 +3883,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
@@ -3924,7 +3939,7 @@
       <c r="G33" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H33" s="32"/>
+      <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
@@ -3946,7 +3961,7 @@
       <c r="G34" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H34" s="32"/>
+      <c r="H34" s="16"/>
     </row>
     <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
@@ -3968,7 +3983,7 @@
       <c r="G35" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
@@ -3990,7 +4005,7 @@
       <c r="G36" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H36" s="32"/>
+      <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
@@ -4012,7 +4027,7 @@
       <c r="G37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H37" s="32"/>
+      <c r="H37" s="16"/>
     </row>
     <row r="38" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -4034,7 +4049,7 @@
       <c r="G38" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H38" s="32"/>
+      <c r="H38" s="16"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
@@ -4056,7 +4071,7 @@
       <c r="G39" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H39" s="32"/>
+      <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
@@ -4078,7 +4093,7 @@
       <c r="G40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H40" s="32"/>
+      <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
@@ -4100,7 +4115,7 @@
       <c r="G41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H41" s="32"/>
+      <c r="H41" s="16"/>
     </row>
     <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
@@ -4122,19 +4137,19 @@
       <c r="G42" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H42" s="32"/>
+      <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
       <c r="G43" s="1" t="s">
         <v>6</v>
       </c>
@@ -4146,13 +4161,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
       <c r="G44" s="9" t="s">
         <v>72</v>
       </c>
@@ -4162,13 +4177,13 @@
       <c r="A45" s="8">
         <v>3</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="25"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="32"/>
       <c r="G45" s="9" t="s">
         <v>133</v>
       </c>
@@ -4178,13 +4193,13 @@
       <c r="A46" s="8">
         <v>3</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
@@ -4234,7 +4249,7 @@
       <c r="G48" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H48" s="32"/>
+      <c r="H48" s="16"/>
     </row>
     <row r="49" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
@@ -4256,7 +4271,7 @@
       <c r="G49" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H49" s="32"/>
+      <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
@@ -4278,7 +4293,7 @@
       <c r="G50" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H50" s="32"/>
+      <c r="H50" s="16"/>
     </row>
     <row r="51" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
@@ -4300,7 +4315,7 @@
       <c r="G51" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="H51" s="32"/>
+      <c r="H51" s="16"/>
     </row>
     <row r="52" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
@@ -4322,7 +4337,7 @@
       <c r="G52" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H52" s="32"/>
+      <c r="H52" s="16"/>
     </row>
     <row r="53" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
@@ -4344,7 +4359,7 @@
       <c r="G53" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H53" s="32"/>
+      <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
@@ -4366,7 +4381,7 @@
       <c r="G54" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H54" s="32"/>
+      <c r="H54" s="16"/>
     </row>
     <row r="55" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
@@ -4388,7 +4403,7 @@
       <c r="G55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H55" s="32"/>
+      <c r="H55" s="16"/>
     </row>
     <row r="56" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
@@ -4410,7 +4425,7 @@
       <c r="G56" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H56" s="32"/>
+      <c r="H56" s="16"/>
     </row>
     <row r="57" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
@@ -4432,20 +4447,19 @@
       <c r="G57" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H57" s="32"/>
+      <c r="H57" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -4457,15 +4471,16 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4494,50 +4509,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4549,13 +4564,13 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="16" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4572,74 +4587,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="18"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="27"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="26"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="31"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4651,13 +4666,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -4665,13 +4680,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="9" t="s">
         <v>118</v>
       </c>
@@ -4681,13 +4696,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -4697,13 +4712,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -4711,13 +4726,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
         <v>110</v>
       </c>
@@ -4727,13 +4742,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -4783,7 +4798,7 @@
       <c r="G18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
@@ -4805,7 +4820,7 @@
       <c r="G19" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
@@ -4827,19 +4842,19 @@
       <c r="G20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" s="11" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
       <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
@@ -4851,13 +4866,13 @@
       <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
       <c r="G22" s="9" t="s">
         <v>116</v>
       </c>
@@ -4867,13 +4882,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
@@ -4923,7 +4938,7 @@
       <c r="G25" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
@@ -4945,7 +4960,7 @@
       <c r="G26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="32"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
@@ -4967,7 +4982,7 @@
       <c r="G27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
@@ -4989,7 +5004,7 @@
       <c r="G28" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H28" s="32"/>
+      <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
@@ -5011,7 +5026,7 @@
       <c r="G29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H29" s="32"/>
+      <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
@@ -5033,7 +5048,7 @@
       <c r="G30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H30" s="32"/>
+      <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
@@ -5055,26 +5070,10 @@
       <c r="G31" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H31" s="32"/>
+      <c r="H31" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
@@ -5084,6 +5083,22 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24CEE40-7404-4AFB-B968-1781631DEA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D10258-0E2E-40EE-A702-6050782588DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23250" yWindow="6450" windowWidth="28365" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="15" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="COPD" sheetId="13" r:id="rId3"/>
     <sheet name="Recruitment" sheetId="14" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="190">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -206,9 +206,6 @@
 }</t>
   </si>
   <si>
-    <t>ShuntFraction</t>
-  </si>
-  <si>
     <t>MechanicalVentilatorHealthy</t>
   </si>
   <si>
@@ -289,9 +286,6 @@
     }</t>
   </si>
   <si>
-    <t>PhysiologicDeadSpaceTidalVolumeRatio</t>
-  </si>
-  <si>
     <t>VD/VT</t>
   </si>
   <si>
@@ -314,12 +308,6 @@
   </si>
   <si>
     <t>QS/QT</t>
-  </si>
-  <si>
-    <t>QS/QT (0.33 +/- 0.15)</t>
-  </si>
-  <si>
-    <t>QS/QT (0.22 +/- 0.14)</t>
   </si>
   <si>
     <t>PaO2/FiO2</t>
@@ -789,6 +777,36 @@
   </si>
   <si>
     <t>{v} = 438</t>
+  </si>
+  <si>
+    <t>ApparentShuntFraction</t>
+  </si>
+  <si>
+    <t>ApparentPhysiologicDeadSpaceTidalVolumeRatio</t>
+  </si>
+  <si>
+    <t>Good:0, Fair:10</t>
+  </si>
+  <si>
+    <t>Good:0, Fair:2</t>
+  </si>
+  <si>
+    <t>ShuntFraction</t>
+  </si>
+  <si>
+    <t>PhysiologicDeadSpaceTidalVolumeRatio</t>
+  </si>
+  <si>
+    <t>VD/VT (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT (determined from blood gas values) (0.33 +/- 0.15)</t>
+  </si>
+  <si>
+    <t>QS/QT (determined from blood gas values) (0.22 +/- 0.14)</t>
   </si>
 </sst>
 </file>
@@ -1051,12 +1069,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1077,6 +1089,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1473,7 +1491,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="11" customWidth="1"/>
@@ -1504,16 +1522,16 @@
     </row>
     <row r="2" spans="1:8" ht="177.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -1540,11 +1558,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -1568,7 +1586,7 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -1577,60 +1595,60 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="26"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1642,13 +1660,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1658,13 +1676,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
     </row>
@@ -1672,15 +1690,15 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H13" s="9"/>
     </row>
@@ -1688,13 +1706,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="B14" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1709,13 +1727,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -1735,10 +1753,10 @@
         <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="12" t="s">
@@ -1757,10 +1775,10 @@
         <v>34</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="12" t="s">
@@ -1779,10 +1797,10 @@
         <v>33</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
@@ -1795,20 +1813,20 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H19" s="16"/>
     </row>
@@ -1817,20 +1835,20 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -1845,14 +1863,14 @@
         <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -1867,12 +1885,14 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" s="10"/>
+        <v>123</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G22" s="12" t="s">
         <v>41</v>
       </c>
@@ -1889,10 +1909,10 @@
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
@@ -1911,10 +1931,10 @@
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
@@ -1933,10 +1953,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
@@ -1955,14 +1975,16 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F26" s="10"/>
+        <v>123</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G26" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H26" s="16"/>
     </row>
@@ -1977,14 +1999,14 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H27" s="16"/>
     </row>
@@ -2027,7 +2049,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="39" style="11" customWidth="1"/>
@@ -2058,16 +2080,16 @@
     </row>
     <row r="2" spans="1:8" ht="241.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -2094,11 +2116,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -2122,7 +2144,7 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -2131,60 +2153,60 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="26"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2210,15 +2232,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="B12" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -2226,13 +2248,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -2242,13 +2264,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -2256,15 +2278,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -2272,13 +2294,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="B16" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -2293,13 +2315,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -2319,10 +2341,10 @@
         <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
@@ -2341,10 +2363,10 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
@@ -2363,10 +2385,10 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
@@ -2379,20 +2401,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -2401,20 +2423,20 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -2429,14 +2451,14 @@
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H23" s="16"/>
     </row>
@@ -2451,12 +2473,14 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F24" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>183</v>
+      </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
       </c>
@@ -2473,12 +2497,14 @@
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G25" s="2" t="s">
         <v>43</v>
       </c>
@@ -2495,12 +2521,14 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G26" s="2" t="s">
         <v>42</v>
       </c>
@@ -2517,12 +2545,14 @@
         <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G27" s="2" t="s">
         <v>44</v>
       </c>
@@ -2539,14 +2569,16 @@
         <v>28</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F28" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H28" s="16"/>
     </row>
@@ -2561,14 +2593,16 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="F29" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H29" s="16"/>
     </row>
@@ -2576,13 +2610,13 @@
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
@@ -2594,15 +2628,15 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
+      <c r="B31" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H31" s="9"/>
     </row>
@@ -2610,15 +2644,15 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
+      <c r="B32" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
       <c r="G32" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H32" s="9"/>
     </row>
@@ -2626,13 +2660,13 @@
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
+      <c r="B33" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -2647,13 +2681,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>6</v>
@@ -2673,10 +2707,10 @@
         <v>34</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
@@ -2695,10 +2729,10 @@
         <v>34</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
@@ -2717,10 +2751,10 @@
         <v>33</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
@@ -2733,20 +2767,20 @@
         <v>23</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -2755,20 +2789,20 @@
         <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H39" s="16"/>
     </row>
@@ -2783,14 +2817,14 @@
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H40" s="16"/>
     </row>
@@ -2805,12 +2839,14 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>183</v>
+      </c>
       <c r="G41" s="12" t="s">
         <v>41</v>
       </c>
@@ -2827,12 +2863,14 @@
         <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F42" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G42" s="2" t="s">
         <v>43</v>
       </c>
@@ -2849,12 +2887,14 @@
         <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F43" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G43" s="2" t="s">
         <v>42</v>
       </c>
@@ -2871,12 +2911,14 @@
         <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F44" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G44" s="2" t="s">
         <v>44</v>
       </c>
@@ -2893,14 +2935,16 @@
         <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F45" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G45" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H45" s="16"/>
     </row>
@@ -2915,14 +2959,16 @@
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="F46" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G46" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H46" s="16"/>
     </row>
@@ -2930,13 +2976,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2948,15 +2994,15 @@
       <c r="A48" s="8">
         <v>3</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
       <c r="G48" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H48" s="9"/>
     </row>
@@ -2964,15 +3010,15 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
+      <c r="B49" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
       <c r="G49" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H49" s="9"/>
     </row>
@@ -2980,13 +3026,13 @@
       <c r="A50" s="8">
         <v>3</v>
       </c>
-      <c r="B50" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
+      <c r="B50" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
@@ -3001,13 +3047,13 @@
         <v>11</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>6</v>
@@ -3027,10 +3073,10 @@
         <v>34</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="12" t="s">
@@ -3049,10 +3095,10 @@
         <v>34</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="12" t="s">
@@ -3071,10 +3117,10 @@
         <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="12" t="s">
@@ -3087,20 +3133,20 @@
         <v>23</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="12" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="H55" s="16"/>
     </row>
@@ -3109,20 +3155,20 @@
         <v>23</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H56" s="16"/>
     </row>
@@ -3137,14 +3183,14 @@
         <v>36</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H57" s="16"/>
     </row>
@@ -3159,12 +3205,14 @@
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F58" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>183</v>
+      </c>
       <c r="G58" s="12" t="s">
         <v>41</v>
       </c>
@@ -3181,12 +3229,14 @@
         <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F59" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G59" s="2" t="s">
         <v>43</v>
       </c>
@@ -3203,12 +3253,14 @@
         <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F60" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G60" s="2" t="s">
         <v>42</v>
       </c>
@@ -3225,12 +3277,14 @@
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F61" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G61" s="2" t="s">
         <v>44</v>
       </c>
@@ -3247,14 +3301,16 @@
         <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F62" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G62" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H62" s="16"/>
     </row>
@@ -3269,14 +3325,14 @@
         <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F63" s="10"/>
       <c r="G63" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H63" s="16"/>
     </row>
@@ -3328,7 +3384,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="39.28515625" style="11" customWidth="1"/>
@@ -3359,16 +3415,16 @@
     </row>
     <row r="2" spans="1:8" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -3395,11 +3451,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3423,7 +3479,7 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -3432,60 +3488,60 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="26"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3497,13 +3553,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3511,15 +3567,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -3527,13 +3583,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -3543,13 +3599,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3557,15 +3613,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -3573,13 +3629,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="B16" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3594,13 +3650,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -3620,10 +3676,10 @@
         <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
@@ -3642,10 +3698,10 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
@@ -3664,10 +3720,10 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
@@ -3680,20 +3736,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -3702,20 +3758,20 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -3730,14 +3786,14 @@
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H23" s="16"/>
     </row>
@@ -3752,12 +3808,14 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F24" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>183</v>
+      </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
       </c>
@@ -3774,12 +3832,14 @@
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G25" s="2" t="s">
         <v>43</v>
       </c>
@@ -3796,12 +3856,14 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G26" s="2" t="s">
         <v>42</v>
       </c>
@@ -3818,12 +3880,14 @@
         <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G27" s="2" t="s">
         <v>44</v>
       </c>
@@ -3833,13 +3897,13 @@
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
@@ -3851,15 +3915,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
+      <c r="B29" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
       <c r="G29" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H29" s="9"/>
     </row>
@@ -3868,14 +3932,14 @@
         <v>2</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="E30" s="31"/>
       <c r="F30" s="32"/>
       <c r="G30" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H30" s="9"/>
     </row>
@@ -3883,13 +3947,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
+      <c r="B31" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
@@ -3904,13 +3968,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>6</v>
@@ -3930,10 +3994,10 @@
         <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
@@ -3952,10 +4016,10 @@
         <v>34</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
@@ -3974,10 +4038,10 @@
         <v>33</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
@@ -3990,20 +4054,20 @@
         <v>23</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="H36" s="16"/>
     </row>
@@ -4012,20 +4076,20 @@
         <v>23</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="2" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H37" s="16"/>
     </row>
@@ -4040,14 +4104,14 @@
         <v>36</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -4062,12 +4126,14 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F39" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>183</v>
+      </c>
       <c r="G39" s="12" t="s">
         <v>41</v>
       </c>
@@ -4084,12 +4150,14 @@
         <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F40" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G40" s="2" t="s">
         <v>43</v>
       </c>
@@ -4106,12 +4174,14 @@
         <v>28</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G41" s="2" t="s">
         <v>42</v>
       </c>
@@ -4128,12 +4198,14 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F42" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G42" s="2" t="s">
         <v>44</v>
       </c>
@@ -4143,13 +4215,13 @@
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
       <c r="G43" s="1" t="s">
         <v>6</v>
       </c>
@@ -4161,15 +4233,15 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
+      <c r="B44" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
       <c r="G44" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H44" s="9"/>
     </row>
@@ -4178,14 +4250,14 @@
         <v>3</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
       <c r="E45" s="31"/>
       <c r="F45" s="32"/>
       <c r="G45" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H45" s="9"/>
     </row>
@@ -4193,13 +4265,13 @@
       <c r="A46" s="8">
         <v>3</v>
       </c>
-      <c r="B46" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
+      <c r="B46" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
@@ -4214,13 +4286,13 @@
         <v>11</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>6</v>
@@ -4240,10 +4312,10 @@
         <v>34</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="12" t="s">
@@ -4262,10 +4334,10 @@
         <v>34</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="12" t="s">
@@ -4284,10 +4356,10 @@
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="12" t="s">
@@ -4300,20 +4372,20 @@
         <v>23</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="12" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="H51" s="16"/>
     </row>
@@ -4322,20 +4394,20 @@
         <v>23</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H52" s="16"/>
     </row>
@@ -4350,14 +4422,14 @@
         <v>36</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H53" s="16"/>
     </row>
@@ -4372,12 +4444,14 @@
         <v>25</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F54" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>183</v>
+      </c>
       <c r="G54" s="12" t="s">
         <v>41</v>
       </c>
@@ -4394,12 +4468,14 @@
         <v>28</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F55" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G55" s="2" t="s">
         <v>43</v>
       </c>
@@ -4416,12 +4492,14 @@
         <v>28</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F56" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G56" s="2" t="s">
         <v>42</v>
       </c>
@@ -4438,12 +4516,14 @@
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F57" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G57" s="2" t="s">
         <v>44</v>
       </c>
@@ -4497,7 +4577,7 @@
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="11" customWidth="1"/>
     <col min="4" max="4" width="25" style="11" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="11" customWidth="1"/>
@@ -4528,16 +4608,16 @@
     </row>
     <row r="2" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -4564,11 +4644,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -4592,7 +4672,7 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -4601,60 +4681,60 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="26"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4680,15 +4760,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="B12" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -4696,13 +4776,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -4712,13 +4792,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -4726,15 +4806,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -4742,13 +4822,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="B16" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -4763,13 +4843,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -4789,14 +4869,14 @@
         <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H18" s="16"/>
     </row>
@@ -4811,14 +4891,16 @@
         <v>28</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H19" s="16"/>
     </row>
@@ -4827,20 +4909,22 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="10"/>
+        <v>61</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -4848,13 +4932,13 @@
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
@@ -4866,15 +4950,15 @@
       <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
+      <c r="B22" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H22" s="9"/>
     </row>
@@ -4882,13 +4966,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
+      <c r="B23" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
@@ -4903,13 +4987,13 @@
         <v>11</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>6</v>
@@ -4929,14 +5013,14 @@
         <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H25" s="16"/>
     </row>
@@ -4951,10 +5035,10 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
@@ -4973,10 +5057,10 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
@@ -4995,14 +5079,16 @@
         <v>28</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" s="10"/>
+        <v>61</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G28" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H28" s="16"/>
     </row>
@@ -5017,14 +5103,14 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H29" s="16"/>
     </row>
@@ -5033,20 +5119,22 @@
         <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F30" s="10"/>
+        <v>61</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="H30" s="16"/>
     </row>
@@ -5055,20 +5143,20 @@
         <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H31" s="16"/>
     </row>

--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D10258-0E2E-40EE-A702-6050782588DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282BEA5A-4BF1-4BDD-A694-8076EAE081CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23250" yWindow="6450" windowWidth="28365" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2175" yWindow="5085" windowWidth="26580" windowHeight="25920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="15" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282BEA5A-4BF1-4BDD-A694-8076EAE081CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3915766-6CD6-459A-9C72-677CCEF16E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2175" yWindow="5085" windowWidth="26580" windowHeight="25920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14430" yWindow="4725" windowWidth="34530" windowHeight="26775" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="15" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="COPD" sheetId="13" r:id="rId3"/>
     <sheet name="Recruitment" sheetId="14" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="189">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -785,12 +785,6 @@
     <t>ApparentPhysiologicDeadSpaceTidalVolumeRatio</t>
   </si>
   <si>
-    <t>Good:0, Fair:10</t>
-  </si>
-  <si>
-    <t>Good:0, Fair:2</t>
-  </si>
-  <si>
     <t>ShuntFraction</t>
   </si>
   <si>
@@ -807,6 +801,9 @@
   </si>
   <si>
     <t>QS/QT (determined from blood gas values) (0.22 +/- 0.14)</t>
+  </si>
+  <si>
+    <t>Good:0, Fair:1</t>
   </si>
 </sst>
 </file>
@@ -1057,17 +1054,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1090,11 +1081,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1503,50 +1500,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="177.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1558,11 +1555,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -1581,74 +1578,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1660,13 +1657,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1676,13 +1673,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
     </row>
@@ -1690,13 +1687,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9" t="s">
         <v>101</v>
       </c>
@@ -1706,13 +1703,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1813,7 +1810,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
@@ -1835,7 +1832,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -1891,7 +1888,7 @@
         <v>123</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>41</v>
@@ -1980,9 +1977,7 @@
       <c r="E26" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
         <v>74</v>
       </c>
@@ -2012,6 +2007,19 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
@@ -2019,19 +2027,6 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2061,50 +2056,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="241.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2116,11 +2111,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -2139,74 +2134,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2232,13 +2227,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
         <v>56</v>
       </c>
@@ -2248,13 +2243,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -2264,13 +2259,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -2278,13 +2273,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
         <v>102</v>
       </c>
@@ -2294,13 +2289,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -2414,7 +2409,7 @@
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -2436,7 +2431,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -2479,7 +2474,7 @@
         <v>75</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -2502,9 +2497,7 @@
       <c r="E25" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
         <v>43</v>
       </c>
@@ -2526,9 +2519,7 @@
       <c r="E26" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
         <v>42</v>
       </c>
@@ -2550,9 +2541,7 @@
       <c r="E27" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
         <v>44</v>
       </c>
@@ -2574,9 +2563,7 @@
       <c r="E28" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F28" s="10"/>
       <c r="G28" s="2" t="s">
         <v>74</v>
       </c>
@@ -2598,9 +2585,7 @@
       <c r="E29" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
         <v>74</v>
       </c>
@@ -2610,13 +2595,13 @@
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
@@ -2628,13 +2613,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
       <c r="G31" s="9" t="s">
         <v>55</v>
       </c>
@@ -2644,13 +2629,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
       <c r="G32" s="9" t="s">
         <v>103</v>
       </c>
@@ -2660,13 +2645,13 @@
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -2780,7 +2765,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -2802,7 +2787,7 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H39" s="16"/>
     </row>
@@ -2845,7 +2830,7 @@
         <v>75</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>41</v>
@@ -2868,9 +2853,7 @@
       <c r="E42" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F42" s="10"/>
       <c r="G42" s="2" t="s">
         <v>43</v>
       </c>
@@ -2892,9 +2875,7 @@
       <c r="E43" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F43" s="10"/>
       <c r="G43" s="2" t="s">
         <v>42</v>
       </c>
@@ -2916,9 +2897,7 @@
       <c r="E44" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F44" s="10"/>
       <c r="G44" s="2" t="s">
         <v>44</v>
       </c>
@@ -2940,9 +2919,7 @@
       <c r="E45" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F45" s="10"/>
       <c r="G45" s="2" t="s">
         <v>74</v>
       </c>
@@ -2964,9 +2941,7 @@
       <c r="E46" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
         <v>74</v>
       </c>
@@ -2976,13 +2951,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2994,13 +2969,13 @@
       <c r="A48" s="8">
         <v>3</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
       <c r="G48" s="9" t="s">
         <v>68</v>
       </c>
@@ -3010,13 +2985,13 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
       <c r="G49" s="9" t="s">
         <v>104</v>
       </c>
@@ -3026,13 +3001,13 @@
       <c r="A50" s="8">
         <v>3</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
@@ -3146,7 +3121,7 @@
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H55" s="16"/>
     </row>
@@ -3168,7 +3143,7 @@
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H56" s="16"/>
     </row>
@@ -3211,7 +3186,7 @@
         <v>75</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>41</v>
@@ -3234,9 +3209,7 @@
       <c r="E59" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F59" s="10"/>
       <c r="G59" s="2" t="s">
         <v>43</v>
       </c>
@@ -3258,9 +3231,7 @@
       <c r="E60" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F60" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F60" s="10"/>
       <c r="G60" s="2" t="s">
         <v>42</v>
       </c>
@@ -3282,9 +3253,7 @@
       <c r="E61" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F61" s="10"/>
       <c r="G61" s="2" t="s">
         <v>44</v>
       </c>
@@ -3306,9 +3275,7 @@
       <c r="E62" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F62" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F62" s="10"/>
       <c r="G62" s="2" t="s">
         <v>74</v>
       </c>
@@ -3338,15 +3305,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -3362,12 +3326,15 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B47:F47"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3396,50 +3363,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3451,11 +3418,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3474,74 +3441,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3553,13 +3520,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3567,13 +3534,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
         <v>57</v>
       </c>
@@ -3583,13 +3550,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -3599,13 +3566,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3613,13 +3580,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
         <v>128</v>
       </c>
@@ -3629,13 +3596,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3749,7 +3716,7 @@
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -3771,7 +3738,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -3814,7 +3781,7 @@
         <v>75</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -3837,9 +3804,7 @@
       <c r="E25" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
         <v>43</v>
       </c>
@@ -3861,9 +3826,7 @@
       <c r="E26" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
         <v>42</v>
       </c>
@@ -3885,9 +3848,7 @@
       <c r="E27" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
         <v>44</v>
       </c>
@@ -3897,13 +3858,13 @@
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
@@ -3915,13 +3876,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
       <c r="G29" s="9" t="s">
         <v>69</v>
       </c>
@@ -3947,13 +3908,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
@@ -4067,7 +4028,7 @@
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H36" s="16"/>
     </row>
@@ -4089,7 +4050,7 @@
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H37" s="16"/>
     </row>
@@ -4132,7 +4093,7 @@
         <v>75</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>41</v>
@@ -4155,9 +4116,7 @@
       <c r="E40" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
         <v>43</v>
       </c>
@@ -4179,9 +4138,7 @@
       <c r="E41" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F41" s="10"/>
       <c r="G41" s="2" t="s">
         <v>42</v>
       </c>
@@ -4203,9 +4160,7 @@
       <c r="E42" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F42" s="10"/>
       <c r="G42" s="2" t="s">
         <v>44</v>
       </c>
@@ -4215,13 +4170,13 @@
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
       <c r="G43" s="1" t="s">
         <v>6</v>
       </c>
@@ -4233,13 +4188,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
       <c r="G44" s="9" t="s">
         <v>70</v>
       </c>
@@ -4265,13 +4220,13 @@
       <c r="A46" s="8">
         <v>3</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
@@ -4385,7 +4340,7 @@
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H51" s="16"/>
     </row>
@@ -4407,7 +4362,7 @@
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H52" s="16"/>
     </row>
@@ -4450,7 +4405,7 @@
         <v>75</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>41</v>
@@ -4473,9 +4428,7 @@
       <c r="E55" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F55" s="10"/>
       <c r="G55" s="2" t="s">
         <v>43</v>
       </c>
@@ -4497,9 +4450,7 @@
       <c r="E56" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F56" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
         <v>42</v>
       </c>
@@ -4521,9 +4472,7 @@
       <c r="E57" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
         <v>44</v>
       </c>
@@ -4531,15 +4480,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -4555,12 +4501,15 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4589,50 +4538,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4644,11 +4593,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -4667,74 +4616,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4760,13 +4709,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
         <v>114</v>
       </c>
@@ -4776,13 +4725,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -4792,13 +4741,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -4806,13 +4755,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
         <v>106</v>
       </c>
@@ -4822,13 +4771,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -4896,9 +4845,7 @@
       <c r="E19" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F19" s="10"/>
       <c r="G19" s="2" t="s">
         <v>107</v>
       </c>
@@ -4920,11 +4867,9 @@
       <c r="E20" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -4932,13 +4877,13 @@
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
@@ -4950,13 +4895,13 @@
       <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
       <c r="G22" s="9" t="s">
         <v>112</v>
       </c>
@@ -4966,13 +4911,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
@@ -5084,9 +5029,7 @@
       <c r="E28" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F28" s="10"/>
       <c r="G28" s="2" t="s">
         <v>108</v>
       </c>
@@ -5130,11 +5073,9 @@
       <c r="E30" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>182</v>
-      </c>
+      <c r="F30" s="10"/>
       <c r="G30" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H30" s="16"/>
     </row>
@@ -5156,12 +5097,28 @@
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H31" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
@@ -5171,22 +5128,6 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3915766-6CD6-459A-9C72-677CCEF16E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E778124C-7364-498D-AE8E-5C4A763C91D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14430" yWindow="4725" windowWidth="34530" windowHeight="26775" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18420" yWindow="3915" windowWidth="34530" windowHeight="26775" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="15" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="188">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -779,12 +779,6 @@
     <t>{v} = 438</t>
   </si>
   <si>
-    <t>ApparentShuntFraction</t>
-  </si>
-  <si>
-    <t>ApparentPhysiologicDeadSpaceTidalVolumeRatio</t>
-  </si>
-  <si>
     <t>ShuntFraction</t>
   </si>
   <si>
@@ -804,6 +798,9 @@
   </si>
   <si>
     <t>Good:0, Fair:1</t>
+  </si>
+  <si>
+    <t>ClinicalShuntFraction</t>
   </si>
 </sst>
 </file>
@@ -1054,11 +1051,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1081,17 +1084,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1500,50 +1497,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="177.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1555,11 +1552,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -1578,74 +1575,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1657,13 +1654,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1673,13 +1670,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
     </row>
@@ -1687,13 +1684,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9" t="s">
         <v>101</v>
       </c>
@@ -1703,13 +1700,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1810,7 +1807,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
@@ -1832,7 +1829,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -1888,7 +1885,7 @@
         <v>123</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>41</v>
@@ -2007,12 +2004,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B3:F3"/>
@@ -2020,13 +2018,12 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2056,50 +2053,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="241.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2111,11 +2108,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -2134,74 +2131,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2227,13 +2224,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
         <v>56</v>
       </c>
@@ -2243,13 +2240,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -2259,13 +2256,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -2273,13 +2270,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
         <v>102</v>
       </c>
@@ -2289,13 +2286,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -2409,7 +2406,7 @@
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -2418,7 +2415,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
@@ -2431,7 +2428,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -2474,7 +2471,7 @@
         <v>75</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -2595,13 +2592,13 @@
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
@@ -2613,13 +2610,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="9" t="s">
         <v>55</v>
       </c>
@@ -2629,13 +2626,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
       <c r="G32" s="9" t="s">
         <v>103</v>
       </c>
@@ -2645,13 +2642,13 @@
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -2765,7 +2762,7 @@
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -2774,7 +2771,7 @@
         <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
@@ -2787,7 +2784,7 @@
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H39" s="16"/>
     </row>
@@ -2830,7 +2827,7 @@
         <v>75</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>41</v>
@@ -2951,13 +2948,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2969,13 +2966,13 @@
       <c r="A48" s="8">
         <v>3</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
       <c r="G48" s="9" t="s">
         <v>68</v>
       </c>
@@ -2985,13 +2982,13 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
       <c r="G49" s="9" t="s">
         <v>104</v>
       </c>
@@ -3001,13 +2998,13 @@
       <c r="A50" s="8">
         <v>3</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
@@ -3121,7 +3118,7 @@
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="12" t="s">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="H55" s="16"/>
     </row>
@@ -3130,7 +3127,7 @@
         <v>23</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
@@ -3143,7 +3140,7 @@
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H56" s="16"/>
     </row>
@@ -3186,7 +3183,7 @@
         <v>75</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>41</v>
@@ -3305,12 +3302,15 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -3326,15 +3326,12 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3363,50 +3360,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3418,11 +3415,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3441,74 +3438,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3520,13 +3517,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3534,13 +3531,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
         <v>57</v>
       </c>
@@ -3550,13 +3547,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -3566,13 +3563,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3580,13 +3577,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
         <v>128</v>
       </c>
@@ -3596,13 +3593,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3716,7 +3713,7 @@
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -3725,7 +3722,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
@@ -3738,7 +3735,7 @@
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -3781,7 +3778,7 @@
         <v>75</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -3858,13 +3855,13 @@
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
@@ -3876,13 +3873,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
       <c r="G29" s="9" t="s">
         <v>69</v>
       </c>
@@ -3908,13 +3905,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
@@ -4028,7 +4025,7 @@
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H36" s="16"/>
     </row>
@@ -4037,7 +4034,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
@@ -4050,7 +4047,7 @@
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H37" s="16"/>
     </row>
@@ -4093,7 +4090,7 @@
         <v>75</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>41</v>
@@ -4170,13 +4167,13 @@
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
       <c r="G43" s="1" t="s">
         <v>6</v>
       </c>
@@ -4188,13 +4185,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
       <c r="G44" s="9" t="s">
         <v>70</v>
       </c>
@@ -4220,13 +4217,13 @@
       <c r="A46" s="8">
         <v>3</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
@@ -4340,7 +4337,7 @@
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="12" t="s">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="H51" s="16"/>
     </row>
@@ -4349,7 +4346,7 @@
         <v>23</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
@@ -4362,7 +4359,7 @@
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H52" s="16"/>
     </row>
@@ -4405,7 +4402,7 @@
         <v>75</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>41</v>
@@ -4480,12 +4477,15 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -4501,15 +4501,12 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4538,50 +4535,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4593,11 +4590,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -4616,74 +4613,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4709,13 +4706,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
         <v>114</v>
       </c>
@@ -4725,13 +4722,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -4741,13 +4738,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -4755,13 +4752,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
         <v>106</v>
       </c>
@@ -4771,13 +4768,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -4856,7 +4853,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -4869,7 +4866,7 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -4877,13 +4874,13 @@
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
@@ -4895,13 +4892,13 @@
       <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="9" t="s">
         <v>112</v>
       </c>
@@ -4911,13 +4908,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
@@ -5062,7 +5059,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
@@ -5075,7 +5072,7 @@
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H30" s="16"/>
     </row>
@@ -5084,7 +5081,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
@@ -5097,28 +5094,12 @@
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H31" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
@@ -5128,6 +5109,22 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E778124C-7364-498D-AE8E-5C4A763C91D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F61106C-2CFA-4E7D-9754-75B72EA344F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18420" yWindow="3915" windowWidth="34530" windowHeight="26775" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29250" yWindow="3375" windowWidth="24480" windowHeight="25620" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="15" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="186">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -305,9 +305,6 @@
   </si>
   <si>
     <t>Ventilated.json</t>
-  </si>
-  <si>
-    <t>QS/QT</t>
   </si>
   <si>
     <t>PaO2/FiO2</t>
@@ -475,15 +472,6 @@
 | PC-CMV | 520   | Adjust         | NA           | NA  | 0.87   | 23       | 18            | 0.5 |</t>
   </si>
   <si>
-    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.4 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.4 }}}]
-  }}
-}</t>
-  </si>
-  <si>
     <t xml:space="preserve">Diagnosis: ARDS
 &lt;br /&gt; </t>
   </si>
@@ -779,9 +767,6 @@
     <t>{v} = 438</t>
   </si>
   <si>
-    <t>ShuntFraction</t>
-  </si>
-  <si>
     <t>PhysiologicDeadSpaceTidalVolumeRatio</t>
   </si>
   <si>
@@ -801,6 +786,15 @@
   </si>
   <si>
     <t>ClinicalShuntFraction</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.5 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.5 }}}]
+  }}
+}</t>
   </si>
 </sst>
 </file>
@@ -1525,7 +1519,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -1580,7 +1574,7 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -1685,14 +1679,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
       <c r="F13" s="28"/>
       <c r="G13" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H13" s="9"/>
     </row>
@@ -1701,7 +1695,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
@@ -1721,13 +1715,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -1747,10 +1741,10 @@
         <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="12" t="s">
@@ -1769,10 +1763,10 @@
         <v>34</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="12" t="s">
@@ -1791,10 +1785,10 @@
         <v>33</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
@@ -1807,16 +1801,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
@@ -1829,20 +1823,20 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -1857,14 +1851,14 @@
         <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -1879,13 +1873,13 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>41</v>
@@ -1903,10 +1897,10 @@
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
@@ -1925,10 +1919,10 @@
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
@@ -1947,10 +1941,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
@@ -1969,14 +1963,14 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H26" s="16"/>
     </row>
@@ -1991,14 +1985,14 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H27" s="16"/>
     </row>
@@ -2081,7 +2075,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -2136,7 +2130,7 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -2271,14 +2265,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
       <c r="E15" s="28"/>
       <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -2287,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
@@ -2307,13 +2301,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -2333,10 +2327,10 @@
         <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
@@ -2355,10 +2349,10 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
@@ -2377,10 +2371,10 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
@@ -2393,20 +2387,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -2415,20 +2409,20 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -2443,14 +2437,14 @@
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H23" s="16"/>
     </row>
@@ -2465,13 +2459,13 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -2489,10 +2483,10 @@
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
@@ -2511,10 +2505,10 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
@@ -2533,10 +2527,10 @@
         <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
@@ -2555,14 +2549,14 @@
         <v>28</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H28" s="16"/>
     </row>
@@ -2577,14 +2571,14 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H29" s="16"/>
     </row>
@@ -2627,14 +2621,14 @@
         <v>2</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C32" s="28"/>
       <c r="D32" s="28"/>
       <c r="E32" s="28"/>
       <c r="F32" s="28"/>
       <c r="G32" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H32" s="9"/>
     </row>
@@ -2643,7 +2637,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
@@ -2663,13 +2657,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>6</v>
@@ -2689,10 +2683,10 @@
         <v>34</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
@@ -2711,10 +2705,10 @@
         <v>34</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
@@ -2733,10 +2727,10 @@
         <v>33</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="12" t="s">
@@ -2749,20 +2743,20 @@
         <v>23</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -2771,20 +2765,20 @@
         <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H39" s="16"/>
     </row>
@@ -2799,14 +2793,14 @@
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H40" s="16"/>
     </row>
@@ -2821,13 +2815,13 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>41</v>
@@ -2845,10 +2839,10 @@
         <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="2" t="s">
@@ -2867,10 +2861,10 @@
         <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="2" t="s">
@@ -2889,10 +2883,10 @@
         <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="2" t="s">
@@ -2911,14 +2905,14 @@
         <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H45" s="16"/>
     </row>
@@ -2933,14 +2927,14 @@
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H46" s="16"/>
     </row>
@@ -2983,14 +2977,14 @@
         <v>3</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
       <c r="E49" s="28"/>
       <c r="F49" s="28"/>
       <c r="G49" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H49" s="9"/>
     </row>
@@ -2999,7 +2993,7 @@
         <v>3</v>
       </c>
       <c r="B50" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50" s="28"/>
       <c r="D50" s="28"/>
@@ -3019,13 +3013,13 @@
         <v>11</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>6</v>
@@ -3045,10 +3039,10 @@
         <v>34</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="12" t="s">
@@ -3067,10 +3061,10 @@
         <v>34</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="12" t="s">
@@ -3089,10 +3083,10 @@
         <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="12" t="s">
@@ -3105,16 +3099,16 @@
         <v>23</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="12" t="s">
@@ -3127,20 +3121,20 @@
         <v>23</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H56" s="16"/>
     </row>
@@ -3155,14 +3149,14 @@
         <v>36</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H57" s="16"/>
     </row>
@@ -3177,13 +3171,13 @@
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>41</v>
@@ -3201,10 +3195,10 @@
         <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="2" t="s">
@@ -3223,10 +3217,10 @@
         <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F60" s="10"/>
       <c r="G60" s="2" t="s">
@@ -3245,10 +3239,10 @@
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F61" s="10"/>
       <c r="G61" s="2" t="s">
@@ -3267,14 +3261,14 @@
         <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F62" s="10"/>
       <c r="G62" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H62" s="16"/>
     </row>
@@ -3289,14 +3283,14 @@
         <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F63" s="10"/>
       <c r="G63" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H63" s="16"/>
     </row>
@@ -3388,7 +3382,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -3443,7 +3437,7 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -3578,14 +3572,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
       <c r="E15" s="28"/>
       <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -3594,7 +3588,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
@@ -3614,13 +3608,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -3640,10 +3634,10 @@
         <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="12" t="s">
@@ -3662,10 +3656,10 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
@@ -3684,10 +3678,10 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="12" t="s">
@@ -3700,20 +3694,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -3722,20 +3716,20 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -3750,14 +3744,14 @@
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H23" s="16"/>
     </row>
@@ -3772,13 +3766,13 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -3796,10 +3790,10 @@
         <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
@@ -3821,7 +3815,7 @@
         <v>71</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
@@ -3840,10 +3834,10 @@
         <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
@@ -3890,14 +3884,14 @@
         <v>2</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="E30" s="31"/>
       <c r="F30" s="32"/>
       <c r="G30" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H30" s="9"/>
     </row>
@@ -3906,7 +3900,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
@@ -3926,13 +3920,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>6</v>
@@ -3952,10 +3946,10 @@
         <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="12" t="s">
@@ -3974,10 +3968,10 @@
         <v>34</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="12" t="s">
@@ -3996,10 +3990,10 @@
         <v>33</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="12" t="s">
@@ -4012,20 +4006,20 @@
         <v>23</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H36" s="16"/>
     </row>
@@ -4034,20 +4028,20 @@
         <v>23</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H37" s="16"/>
     </row>
@@ -4062,14 +4056,14 @@
         <v>36</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -4084,13 +4078,13 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>41</v>
@@ -4108,10 +4102,10 @@
         <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
@@ -4133,7 +4127,7 @@
         <v>71</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="2" t="s">
@@ -4152,10 +4146,10 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="2" t="s">
@@ -4202,14 +4196,14 @@
         <v>3</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
       <c r="E45" s="31"/>
       <c r="F45" s="32"/>
       <c r="G45" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H45" s="9"/>
     </row>
@@ -4218,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C46" s="28"/>
       <c r="D46" s="28"/>
@@ -4238,13 +4232,13 @@
         <v>11</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>6</v>
@@ -4264,10 +4258,10 @@
         <v>34</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="12" t="s">
@@ -4286,10 +4280,10 @@
         <v>34</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="12" t="s">
@@ -4308,10 +4302,10 @@
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="12" t="s">
@@ -4324,16 +4318,16 @@
         <v>23</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="12" t="s">
@@ -4346,20 +4340,20 @@
         <v>23</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H52" s="16"/>
     </row>
@@ -4374,14 +4368,14 @@
         <v>36</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H53" s="16"/>
     </row>
@@ -4396,13 +4390,13 @@
         <v>25</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>41</v>
@@ -4420,10 +4414,10 @@
         <v>28</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="2" t="s">
@@ -4445,7 +4439,7 @@
         <v>71</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
@@ -4464,10 +4458,10 @@
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
@@ -4560,10 +4554,10 @@
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
@@ -4618,7 +4612,7 @@
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H5" s="17"/>
     </row>
@@ -4707,14 +4701,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>113</v>
+        <v>185</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
       <c r="E12" s="28"/>
       <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -4753,14 +4747,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C15" s="28"/>
       <c r="D15" s="28"/>
       <c r="E15" s="28"/>
       <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -4769,7 +4763,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
@@ -4789,13 +4783,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -4815,14 +4809,14 @@
         <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H18" s="16"/>
     </row>
@@ -4844,7 +4838,7 @@
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H19" s="16"/>
     </row>
@@ -4853,7 +4847,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -4866,7 +4860,7 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -4893,14 +4887,14 @@
         <v>2</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C22" s="28"/>
       <c r="D22" s="28"/>
       <c r="E22" s="28"/>
       <c r="F22" s="28"/>
       <c r="G22" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H22" s="9"/>
     </row>
@@ -4909,7 +4903,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
@@ -4929,13 +4923,13 @@
         <v>11</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>6</v>
@@ -4955,14 +4949,14 @@
         <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H25" s="16"/>
     </row>
@@ -4977,7 +4971,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>62</v>
@@ -4999,7 +4993,7 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>61</v>
@@ -5028,7 +5022,7 @@
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H28" s="16"/>
     </row>
@@ -5043,14 +5037,14 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H29" s="16"/>
     </row>
@@ -5059,7 +5053,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
@@ -5072,7 +5066,7 @@
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H30" s="16"/>
     </row>
@@ -5081,20 +5075,20 @@
         <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H31" s="16"/>
     </row>

--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F61106C-2CFA-4E7D-9754-75B72EA344F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4A8BAC-7AA9-4F23-9F7C-F67EA34D4373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29250" yWindow="3375" windowWidth="24480" windowHeight="25620" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18165" yWindow="4560" windowWidth="32130" windowHeight="24720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="15" r:id="rId1"/>
@@ -452,19 +452,6 @@
 }</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "ContinuousMandatoryVentilation", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.87, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 22, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 23, "Unit": "1/min" } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>PEEP is increased for improved recruitment with PIP set to maintain target TV:
 &lt;br /&gt;
 | Mode   | VT (mL) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
@@ -746,12 +733,6 @@
     <t>{v} = {1}</t>
   </si>
   <si>
-    <t>{v} &gt; 1</t>
-  </si>
-  <si>
-    <t>{v} &lt; 1</t>
-  </si>
-  <si>
     <t>{v} = 18</t>
   </si>
   <si>
@@ -794,6 +775,24 @@
       { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.5 }}},
       { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.5 }}}]
   }}
+}</t>
+  </si>
+  <si>
+    <t>{v} &gt; {1}</t>
+  </si>
+  <si>
+    <t>{v} &lt; {1}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "ContinuousMandatoryVentilation", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.87, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 22, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 23, "Unit": "1/min" } }
 }</t>
   </si>
 </sst>
@@ -1045,17 +1044,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1078,11 +1071,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1491,50 +1490,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="177.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1546,11 +1545,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -1569,74 +1568,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="17"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1648,13 +1647,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1664,13 +1663,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
     </row>
@@ -1678,13 +1677,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9" t="s">
         <v>100</v>
       </c>
@@ -1694,13 +1693,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1715,13 +1714,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -1741,7 +1740,7 @@
         <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>74</v>
@@ -1763,7 +1762,7 @@
         <v>34</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -1785,7 +1784,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>75</v>
@@ -1801,16 +1800,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
@@ -1823,20 +1822,20 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -1851,14 +1850,14 @@
         <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -1873,13 +1872,13 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>41</v>
@@ -1897,10 +1896,10 @@
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
@@ -1919,10 +1918,10 @@
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
@@ -1941,10 +1940,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
@@ -1963,10 +1962,10 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
@@ -1985,10 +1984,10 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
@@ -1998,6 +1997,19 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
@@ -2005,19 +2017,6 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2047,50 +2046,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="241.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2102,11 +2101,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -2125,74 +2124,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="17"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2218,13 +2217,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
         <v>56</v>
       </c>
@@ -2234,13 +2233,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -2250,13 +2249,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -2264,13 +2263,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="B15" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
         <v>101</v>
       </c>
@@ -2280,13 +2279,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -2301,13 +2300,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -2327,7 +2326,7 @@
         <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>74</v>
@@ -2349,7 +2348,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>74</v>
@@ -2371,7 +2370,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>75</v>
@@ -2387,20 +2386,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>75</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -2409,20 +2408,20 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -2437,14 +2436,14 @@
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H23" s="16"/>
     </row>
@@ -2465,7 +2464,7 @@
         <v>74</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -2571,10 +2570,10 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
@@ -2586,13 +2585,13 @@
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
@@ -2604,13 +2603,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
       <c r="G31" s="9" t="s">
         <v>55</v>
       </c>
@@ -2620,13 +2619,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
+      <c r="B32" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
       <c r="G32" s="9" t="s">
         <v>102</v>
       </c>
@@ -2636,13 +2635,13 @@
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -2657,13 +2656,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>6</v>
@@ -2683,7 +2682,7 @@
         <v>34</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>74</v>
@@ -2705,7 +2704,7 @@
         <v>34</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>74</v>
@@ -2727,7 +2726,7 @@
         <v>33</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>75</v>
@@ -2743,20 +2742,20 @@
         <v>23</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>75</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -2765,20 +2764,20 @@
         <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H39" s="16"/>
     </row>
@@ -2793,14 +2792,14 @@
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H40" s="16"/>
     </row>
@@ -2821,7 +2820,7 @@
         <v>74</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>41</v>
@@ -2927,10 +2926,10 @@
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
@@ -2942,13 +2941,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2960,13 +2959,13 @@
       <c r="A48" s="8">
         <v>3</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
       <c r="G48" s="9" t="s">
         <v>68</v>
       </c>
@@ -2976,13 +2975,13 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
+      <c r="B49" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
       <c r="G49" s="9" t="s">
         <v>103</v>
       </c>
@@ -2992,13 +2991,13 @@
       <c r="A50" s="8">
         <v>3</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
@@ -3013,13 +3012,13 @@
         <v>11</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>6</v>
@@ -3039,7 +3038,7 @@
         <v>34</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>74</v>
@@ -3061,7 +3060,7 @@
         <v>34</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>74</v>
@@ -3083,7 +3082,7 @@
         <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>75</v>
@@ -3099,13 +3098,13 @@
         <v>23</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>75</v>
@@ -3121,20 +3120,20 @@
         <v>23</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H56" s="16"/>
     </row>
@@ -3149,14 +3148,14 @@
         <v>36</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H57" s="16"/>
     </row>
@@ -3177,7 +3176,7 @@
         <v>74</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>41</v>
@@ -3283,10 +3282,10 @@
         <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F63" s="10"/>
       <c r="G63" s="2" t="s">
@@ -3296,15 +3295,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -3320,12 +3316,15 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B47:F47"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3354,50 +3353,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3409,11 +3408,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3432,74 +3431,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="17"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3511,13 +3510,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3525,13 +3524,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
         <v>57</v>
       </c>
@@ -3541,13 +3540,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -3557,13 +3556,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3571,15 +3570,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="B15" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -3587,13 +3586,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3608,13 +3607,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -3634,7 +3633,7 @@
         <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>78</v>
@@ -3656,7 +3655,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>77</v>
@@ -3678,7 +3677,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>74</v>
@@ -3694,20 +3693,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -3716,20 +3715,20 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>80</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -3744,14 +3743,14 @@
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H23" s="16"/>
     </row>
@@ -3772,7 +3771,7 @@
         <v>74</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -3849,13 +3848,13 @@
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
@@ -3867,13 +3866,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
       <c r="G29" s="9" t="s">
         <v>69</v>
       </c>
@@ -3884,7 +3883,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
@@ -3899,13 +3898,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
@@ -3920,13 +3919,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>6</v>
@@ -3946,7 +3945,7 @@
         <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>78</v>
@@ -3968,7 +3967,7 @@
         <v>34</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>77</v>
@@ -3990,7 +3989,7 @@
         <v>33</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>74</v>
@@ -4006,20 +4005,20 @@
         <v>23</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H36" s="16"/>
     </row>
@@ -4028,20 +4027,20 @@
         <v>23</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>80</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H37" s="16"/>
     </row>
@@ -4056,14 +4055,14 @@
         <v>36</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -4084,7 +4083,7 @@
         <v>74</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>41</v>
@@ -4161,13 +4160,13 @@
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
       <c r="G43" s="1" t="s">
         <v>6</v>
       </c>
@@ -4179,13 +4178,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
       <c r="G44" s="9" t="s">
         <v>70</v>
       </c>
@@ -4196,14 +4195,14 @@
         <v>3</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
       <c r="E45" s="31"/>
       <c r="F45" s="32"/>
       <c r="G45" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H45" s="9"/>
     </row>
@@ -4211,13 +4210,13 @@
       <c r="A46" s="8">
         <v>3</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
@@ -4232,13 +4231,13 @@
         <v>11</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>6</v>
@@ -4258,7 +4257,7 @@
         <v>34</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>78</v>
@@ -4280,7 +4279,7 @@
         <v>34</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>77</v>
@@ -4302,7 +4301,7 @@
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>74</v>
@@ -4318,13 +4317,13 @@
         <v>23</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>79</v>
@@ -4340,20 +4339,20 @@
         <v>23</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H52" s="16"/>
     </row>
@@ -4368,14 +4367,14 @@
         <v>36</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H53" s="16"/>
     </row>
@@ -4396,7 +4395,7 @@
         <v>74</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>41</v>
@@ -4471,15 +4470,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -4495,12 +4491,15 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4529,50 +4528,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4584,11 +4583,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -4607,74 +4606,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="17"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4700,15 +4699,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="B12" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -4716,13 +4715,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -4732,27 +4731,27 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" ht="187.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="B15" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
         <v>105</v>
       </c>
@@ -4762,13 +4761,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -4783,13 +4782,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -4809,14 +4808,14 @@
         <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H18" s="16"/>
     </row>
@@ -4847,7 +4846,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -4860,7 +4859,7 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -4868,13 +4867,13 @@
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
@@ -4882,19 +4881,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="187.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="172.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
+      <c r="B22" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
       <c r="G22" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H22" s="9"/>
     </row>
@@ -4902,13 +4901,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
@@ -4923,13 +4922,13 @@
         <v>11</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>6</v>
@@ -4949,14 +4948,14 @@
         <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H25" s="16"/>
     </row>
@@ -4971,7 +4970,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>62</v>
@@ -4993,7 +4992,7 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>61</v>
@@ -5037,7 +5036,7 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>61</v>
@@ -5053,7 +5052,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
@@ -5066,7 +5065,7 @@
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H30" s="16"/>
     </row>
@@ -5075,25 +5074,41 @@
         <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H31" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
@@ -5103,22 +5118,6 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4A8BAC-7AA9-4F23-9F7C-F67EA34D4373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50F78EB-1E72-4485-B628-A41CE8EE377B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18165" yWindow="4560" windowWidth="32130" windowHeight="24720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -793,6 +793,7 @@
   "InspiratoryPressure": { "ScalarPressure": { "Value": 22, "Unit": "cmH2O" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 23, "Unit": "1/min" } }
+  }}
 }</t>
   </si>
 </sst>
@@ -1044,11 +1045,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1071,17 +1078,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1490,50 +1491,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="177.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1545,11 +1546,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -1568,74 +1569,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1647,13 +1648,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1663,13 +1664,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
     </row>
@@ -1677,13 +1678,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9" t="s">
         <v>100</v>
       </c>
@@ -1693,13 +1694,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1997,12 +1998,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B3:F3"/>
@@ -2010,13 +2012,12 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2046,50 +2047,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="241.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2101,11 +2102,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -2124,74 +2125,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2217,13 +2218,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
         <v>56</v>
       </c>
@@ -2233,13 +2234,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -2249,13 +2250,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -2263,13 +2264,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
         <v>101</v>
       </c>
@@ -2279,13 +2280,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -2585,13 +2586,13 @@
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
@@ -2603,13 +2604,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="9" t="s">
         <v>55</v>
       </c>
@@ -2619,13 +2620,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
       <c r="G32" s="9" t="s">
         <v>102</v>
       </c>
@@ -2635,13 +2636,13 @@
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -2941,13 +2942,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2959,13 +2960,13 @@
       <c r="A48" s="8">
         <v>3</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
       <c r="G48" s="9" t="s">
         <v>68</v>
       </c>
@@ -2975,13 +2976,13 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
       <c r="G49" s="9" t="s">
         <v>103</v>
       </c>
@@ -2991,13 +2992,13 @@
       <c r="A50" s="8">
         <v>3</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
@@ -3295,12 +3296,15 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -3316,15 +3320,12 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3353,50 +3354,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3408,11 +3409,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3431,74 +3432,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3510,13 +3511,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3524,13 +3525,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
         <v>57</v>
       </c>
@@ -3540,13 +3541,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -3556,13 +3557,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3570,13 +3571,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
         <v>125</v>
       </c>
@@ -3586,13 +3587,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3848,13 +3849,13 @@
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
@@ -3866,13 +3867,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
       <c r="G29" s="9" t="s">
         <v>69</v>
       </c>
@@ -3898,13 +3899,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
@@ -4160,13 +4161,13 @@
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
       <c r="G43" s="1" t="s">
         <v>6</v>
       </c>
@@ -4178,13 +4179,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
       <c r="G44" s="9" t="s">
         <v>70</v>
       </c>
@@ -4210,13 +4211,13 @@
       <c r="A46" s="8">
         <v>3</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
@@ -4470,12 +4471,15 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -4491,15 +4495,12 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4528,50 +4529,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="26"/>
+      <c r="D1" s="17"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4583,11 +4584,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -4606,74 +4607,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="26"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4699,13 +4700,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
       <c r="G12" s="9" t="s">
         <v>111</v>
       </c>
@@ -4715,13 +4716,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -4731,27 +4732,27 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
-    <row r="15" spans="1:8" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="183" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="9" t="s">
         <v>105</v>
       </c>
@@ -4761,13 +4762,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -4867,13 +4868,13 @@
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
       <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
@@ -4885,13 +4886,13 @@
       <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="9" t="s">
         <v>110</v>
       </c>
@@ -4901,13 +4902,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
@@ -5093,22 +5094,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
@@ -5118,6 +5103,22 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
+++ b/data/human/adult/validation/Scenarios/MechanicalVentilator/MechanicalVentilator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\MechanicalVentilator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50F78EB-1E72-4485-B628-A41CE8EE377B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6BE364-04D7-4B81-B944-D6DADB4E2C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18165" yWindow="4560" windowWidth="32130" windowHeight="24720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Healthy" sheetId="15" r:id="rId1"/>
@@ -439,19 +439,6 @@
     <t>A standard patient is mechanically ventilated with moderate ARDS. The PEEP is increased to test the effects of improved lung recruitment. Ventilator setting and expected values were largely determined from Karbing et al @cite karbing2020changes Table 2.</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "ContinuousMandatoryVentilation", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.26 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.3, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 14, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 17, "Unit": "1/min" } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>PEEP is increased for improved recruitment with PIP set to maintain target TV:
 &lt;br /&gt;
 | Mode   | VT (mL) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
@@ -463,8 +450,238 @@
 &lt;br /&gt; </t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+    <t>[200, 300]</t>
+  </si>
+  <si>
+    <t>ferguson2012berlin</t>
+  </si>
+  <si>
+    <t>[100, 200]</t>
+  </si>
+  <si>
+    <t>[0.2, 0.4]</t>
+  </si>
+  <si>
+    <t>kacmarek2016egan</t>
+  </si>
+  <si>
+    <t>[400, 500]</t>
+  </si>
+  <si>
+    <t>[7.35, 7.45]</t>
+  </si>
+  <si>
+    <t>VT (measured)</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 7.3 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (mL) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| PC-CMV | 438   | Adjust         | NA           | 0.32  | 1.2   | 15       | 5            | 0.32 |</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 10.0 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (mL) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| PC-CMV | 600   | Adjust         | NA           | 0.5  | 1.1   | 14       | 10            | 0.42 |</t>
+  </si>
+  <si>
+    <t>maj2023ventilatory,torres1989ventilation</t>
+  </si>
+  <si>
+    <t>A healthy male patient with a predicted body weight of 60 kg is mechanically ventilated.  These are the data sources:
+ - Resistance: Inspiratory resistance (Rinsp) is assumed equal to expiratory resistance (Rexp), taken from Arnal et al @cite arnal2018parameters (Table 9).
+ - Compliance: Taken from Arnal et al @cite arnal2018parameters (Table 3). 
+ - Dead space:  Standard healthy values taken from the Kacmarek et al Fundamentals of Respiratory Care page 63 @cite kacmarek2016egan.
+ - Shunt:  Standard healthy values taken from the Kacmarek et al Fundamentals of Respiratory Care page 68 @cite kacmarek2016egan.
+ - Ventilator Settings: All ventilator settings were takeng from Arnal et al @cite arnal2018parameters (Table 2) for a male patient aged 73 years and predicted body weight of 60 kg. Note that the mode for simulation is PC-CMV, which is equivalent to the mode used by Arnal et @cite arnal2018parameters for passive pateints. Equivalent settings for tidal volume, rate, and inspiratory time can be used for volume control simulations.
+ - Blood Gas Values: Standard healthy values taken from the Kacmarek et al Fundamentals of Respiratory Care @cite kacmarek2016egan.</t>
+  </si>
+  <si>
+    <t>A male patient with a predicted body weight of 60 kg is mechanically ventilated with varying severities of ARDS.  These are the data sources:
+ - Resistance: Rinsp is assumed equal to Rexp, taken from Arnal et al @cite arnal2018parameters (Table 3).
+ - Compliance: All compliances were taken from Maj et al @cite maj2023ventilatory (Table 1) derived as tidal volume (ie, mL/kg x PBW calcualted with ARDS equation for males) divided by driving pressure. Mild ARDS was mean minus 1  standard deviatio; moderate ARDS was the mean value; severe ARDS was mean plus 1  standard deviation. 
+ - Dead space:  VD/VT values were taken from Maj et al @cite maj2023ventilatory (Table 2). 
+ - Shunt:  Values for QS/QT were a compromise between Maj et al @cite maj2023ventilatory (Table 2, venous admixture) and Torres et al @cite torres1989ventilation (Table 3) to give realistic PO2 results for the simulated ventilator settings.    
+ - Ventilator Settings: All ventilator settings were takeng from Arnal et al @cite arnal2018parameters (Table 2) for a male patient aged 73 years and predicted body weight of 60 kg. Note that the mode for simulation is PC-CMV, which is equivalent to the mode used by Arnal et @cite arnal2018parameters for passive pateints. Equivalent settings for tidal volume, rate, and inspiratory time can be used for volume control simulations.
+ - Blood Gas Values: Expected blood gas value for outputs of Pulse simulator were taken from the most complete source: Arnal et al @cite arnal2018parameters (Table 2). FiO2 values for moderate and severe ARDS were adjusted upward to give the expected P/F ratios for the given PaO2 ranges. Expected values for SpO2 were calculated from PaO2 using the equation from Gadrey et al @cite gadrey2019imputation.</t>
+  </si>
+  <si>
+    <t>A male patient with a predicted body weight of 60 kg is mechanically ventilated with varying severities of COPD. These are the data sources:
+ - Resistance: A regression equation was derived from the data of van den Berg et al @cite van1991effects that predicts Rexp from measured FEV1. Then Rinsp is calculated as 65% of Rexp (from Officer et al @cite officer1998measurement). Using the FEV1 calculator, the Rinsp value for mild COPD was based on predicted FEV1 of a 25 year old male, which showed that it was not different from healthy or ARDS patients. The Rexp value for moderate COPD was based on 60 year old male with 41% pred FEV1 = Gold Stage 3. The Rexp value for severe COPD was based on a 60 year old male with 28% pred FEV1 = Gold Stage 4.
+ - Compliance: All compliances were taken from Arnal et al @cite arnal2018parameters (Table 3). Mild COPD was approximately the mean value (so as to be higher than normal); moderate COPD was the average of the mean and the high end of the range (60,75), and severe COPD was the highest value of the range.
+ - Dead space:  VD/VT values were taken from Farah et al @cite farah2009can (Table 1). Mild COPD was mean minus 1 standard deviation; moderate COPD was the mean value; severe COPD was mean plus 2 standard deviations. 
+ - Shunt: QS/QT values were taken from Torres et al @cite torres1989ventilation (Table 3). Mild COPD was mean minus 2 standard deviations; moderate COPD was the mean value; for severe COPD, values for FiO2 and PaO2 were taken from Arnal et al @cite arnal2018parameters (Table 2) and used with various prediction equations for iso-shunt lines to get a match at about PaO2 = 69, FiO2 = 0.4 and shunt = 0.20 .
+ - Ventilator Settings: All ventilator settings were takeng from Arnal et al @cite arnal2018parameters (Table 2) for a male patient aged 73 years and predicted body weight of 60 kg. Note that the mode for simulation is PC-CMV, which is equivalent to the mode used by Arnal et @cite arnal2018parameters for passive pateints. Equivalent settings for tidal volume, rate, and inspiratory time can be used for volume control simulations.
+ - Blood Gas Values: Expected blood gas value for outputs of Pulse simulator were taken from the most complete source: Arnal et al @cite arnal2018parameters (Table 2). Expected values for SpO2 were calculated from PaO2 using the equation from Gadrey et al @cite gadrey2019imputation.</t>
+  </si>
+  <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>{v} = 10</t>
+  </si>
+  <si>
+    <t>{v} = 54</t>
+  </si>
+  <si>
+    <t>{v} &lt; 0.05</t>
+  </si>
+  <si>
+    <t>{v} = 444</t>
+  </si>
+  <si>
+    <t>{v} &gt; 75</t>
+  </si>
+  <si>
+    <t>{v} &lt; 45</t>
+  </si>
+  <si>
+    <t>{v} &gt; 0.95</t>
+  </si>
+  <si>
+    <t>{v} &gt; 300</t>
+  </si>
+  <si>
+    <t>Comparison Formula</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>{v} = 12</t>
+  </si>
+  <si>
+    <t>{v} = 40</t>
+  </si>
+  <si>
+    <t>{v} = 0.54</t>
+  </si>
+  <si>
+    <t>{v} = 0.2</t>
+  </si>
+  <si>
+    <t>{v} = 414</t>
+  </si>
+  <si>
+    <t>{v} = 35</t>
+  </si>
+  <si>
+    <t>{v} = 0.57</t>
+  </si>
+  <si>
+    <t>{v} = 0.3</t>
+  </si>
+  <si>
+    <t>{v} = 396</t>
+  </si>
+  <si>
+    <t>{v} = 33</t>
+  </si>
+  <si>
+    <t>{v} = 0.65</t>
+  </si>
+  <si>
+    <t>{v} = 0.4</t>
+  </si>
+  <si>
+    <t>{v} &lt; 100</t>
+  </si>
+  <si>
+    <t>{v} = 24</t>
+  </si>
+  <si>
+    <t>{v} = 36</t>
+  </si>
+  <si>
+    <t>{v} = 68</t>
+  </si>
+  <si>
+    <t>{v} = 0.49</t>
+  </si>
+  <si>
+    <t>{v} = 0.19</t>
+  </si>
+  <si>
+    <t>{v} = 534</t>
+  </si>
+  <si>
+    <t>{v} = 34</t>
+  </si>
+  <si>
+    <t>{v} = 51</t>
+  </si>
+  <si>
+    <t>{v} = 75</t>
+  </si>
+  <si>
+    <t>{v} = 0.73</t>
+  </si>
+  <si>
+    <t>{v} = 600</t>
+  </si>
+  <si>
+    <t>{v} = 520</t>
+  </si>
+  <si>
+    <t>{v} = {1}</t>
+  </si>
+  <si>
+    <t>{v} = 18</t>
+  </si>
+  <si>
+    <t>{v} = 60</t>
+  </si>
+  <si>
+    <t>{v} = 0.37</t>
+  </si>
+  <si>
+    <t>{v} = 0.12</t>
+  </si>
+  <si>
+    <t>{v} = 438</t>
+  </si>
+  <si>
+    <t>PhysiologicDeadSpaceTidalVolumeRatio</t>
+  </si>
+  <si>
+    <t>VD/VT (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT (determined from blood gas values)</t>
+  </si>
+  <si>
+    <t>QS/QT (determined from blood gas values) (0.33 +/- 0.15)</t>
+  </si>
+  <si>
+    <t>QS/QT (determined from blood gas values) (0.22 +/- 0.14)</t>
+  </si>
+  <si>
+    <t>Good:0, Fair:1</t>
+  </si>
+  <si>
+    <t>ClinicalShuntFraction</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.5 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.5 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{v} &gt; {1}</t>
+  </si>
+  <si>
+    <t>{v} &lt; {1}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": {
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
   "Mode": "ContinuousMandatoryVentilation", 
   "InspirationWaveform": "Square",
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
@@ -472,12 +689,64 @@
   "InspiratoryPressure": { "ScalarPressure": { "Value": 34, "Unit": "cmH2O" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 18, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 23, "Unit": "1/min" } }
+  }
+}}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { 
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
+  "Mode": "ContinuousMandatoryVentilation", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.87, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 22, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 23, "Unit": "1/min" } }
+  }
+}}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { 
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
+  "Mode": "ContinuousMandatoryVentilation", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.42 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.1, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 40, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } }
   }}
 }</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { 
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
+  "Mode": "ContinuousMandatoryVentilation", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.32 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.3, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 25, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 7, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { 
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
+  "Mode": "ContinuousMandatoryVentilation", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.28 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.2, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 15, "Unit": "1/min" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { 
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
   "Mode": "ContinuousMandatoryVentilation", 
   "InspirationWaveform": "Square",
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.31 } },
@@ -489,8 +758,8 @@
 }</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { 
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
   "Mode": "ContinuousMandatoryVentilation", 
   "InspirationWaveform": "Square",
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.50 } },
@@ -502,17 +771,8 @@
 }</t>
   </si>
   <si>
-    <t>[200, 300]</t>
-  </si>
-  <si>
-    <t>ferguson2012berlin</t>
-  </si>
-  <si>
-    <t>[100, 200]</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { 
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
   "Mode": "ContinuousMandatoryVentilation", 
   "InspirationWaveform": "Square",
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.80 } },
@@ -524,275 +784,15 @@
 }</t>
   </si>
   <si>
-    <t>[0.2, 0.4]</t>
-  </si>
-  <si>
-    <t>kacmarek2016egan</t>
-  </si>
-  <si>
-    <t>[400, 500]</t>
-  </si>
-  <si>
-    <t>[7.35, 7.45]</t>
-  </si>
-  <si>
-    <t>VT (measured)</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { 
+  "MechanicalVentilatorMode": { "SupplementalSettings": {"Connection": "On" }},
   "Mode": "ContinuousMandatoryVentilation", 
   "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.32 } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.26 } },
   "InspiratoryPeriod": { "ScalarTime": { "Value": 1.3, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 25, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 7, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Ventilator settings are (VT Target = 7.3 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (mL) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | 438   | Adjust         | NA           | 0.32  | 1.2   | 15       | 5            | 0.32 |</t>
-  </si>
-  <si>
-    <t>Ventilator settings are (VT Target = 10.0 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (mL) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | 600   | Adjust         | NA           | 0.5  | 1.1   | 14       | 10            | 0.42 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "ContinuousMandatoryVentilation", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.28 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.2, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 14, "Unit": "cmH2O" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 15, "Unit": "1/min" } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "ContinuousMandatoryVentilation", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.42 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.1, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 40, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 14, "Unit": "1/min" } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>maj2023ventilatory,torres1989ventilation</t>
-  </si>
-  <si>
-    <t>A healthy male patient with a predicted body weight of 60 kg is mechanically ventilated.  These are the data sources:
- - Resistance: Inspiratory resistance (Rinsp) is assumed equal to expiratory resistance (Rexp), taken from Arnal et al @cite arnal2018parameters (Table 9).
- - Compliance: Taken from Arnal et al @cite arnal2018parameters (Table 3). 
- - Dead space:  Standard healthy values taken from the Kacmarek et al Fundamentals of Respiratory Care page 63 @cite kacmarek2016egan.
- - Shunt:  Standard healthy values taken from the Kacmarek et al Fundamentals of Respiratory Care page 68 @cite kacmarek2016egan.
- - Ventilator Settings: All ventilator settings were takeng from Arnal et al @cite arnal2018parameters (Table 2) for a male patient aged 73 years and predicted body weight of 60 kg. Note that the mode for simulation is PC-CMV, which is equivalent to the mode used by Arnal et @cite arnal2018parameters for passive pateints. Equivalent settings for tidal volume, rate, and inspiratory time can be used for volume control simulations.
- - Blood Gas Values: Standard healthy values taken from the Kacmarek et al Fundamentals of Respiratory Care @cite kacmarek2016egan.</t>
-  </si>
-  <si>
-    <t>A male patient with a predicted body weight of 60 kg is mechanically ventilated with varying severities of ARDS.  These are the data sources:
- - Resistance: Rinsp is assumed equal to Rexp, taken from Arnal et al @cite arnal2018parameters (Table 3).
- - Compliance: All compliances were taken from Maj et al @cite maj2023ventilatory (Table 1) derived as tidal volume (ie, mL/kg x PBW calcualted with ARDS equation for males) divided by driving pressure. Mild ARDS was mean minus 1  standard deviatio; moderate ARDS was the mean value; severe ARDS was mean plus 1  standard deviation. 
- - Dead space:  VD/VT values were taken from Maj et al @cite maj2023ventilatory (Table 2). 
- - Shunt:  Values for QS/QT were a compromise between Maj et al @cite maj2023ventilatory (Table 2, venous admixture) and Torres et al @cite torres1989ventilation (Table 3) to give realistic PO2 results for the simulated ventilator settings.    
- - Ventilator Settings: All ventilator settings were takeng from Arnal et al @cite arnal2018parameters (Table 2) for a male patient aged 73 years and predicted body weight of 60 kg. Note that the mode for simulation is PC-CMV, which is equivalent to the mode used by Arnal et @cite arnal2018parameters for passive pateints. Equivalent settings for tidal volume, rate, and inspiratory time can be used for volume control simulations.
- - Blood Gas Values: Expected blood gas value for outputs of Pulse simulator were taken from the most complete source: Arnal et al @cite arnal2018parameters (Table 2). FiO2 values for moderate and severe ARDS were adjusted upward to give the expected P/F ratios for the given PaO2 ranges. Expected values for SpO2 were calculated from PaO2 using the equation from Gadrey et al @cite gadrey2019imputation.</t>
-  </si>
-  <si>
-    <t>A male patient with a predicted body weight of 60 kg is mechanically ventilated with varying severities of COPD. These are the data sources:
- - Resistance: A regression equation was derived from the data of van den Berg et al @cite van1991effects that predicts Rexp from measured FEV1. Then Rinsp is calculated as 65% of Rexp (from Officer et al @cite officer1998measurement). Using the FEV1 calculator, the Rinsp value for mild COPD was based on predicted FEV1 of a 25 year old male, which showed that it was not different from healthy or ARDS patients. The Rexp value for moderate COPD was based on 60 year old male with 41% pred FEV1 = Gold Stage 3. The Rexp value for severe COPD was based on a 60 year old male with 28% pred FEV1 = Gold Stage 4.
- - Compliance: All compliances were taken from Arnal et al @cite arnal2018parameters (Table 3). Mild COPD was approximately the mean value (so as to be higher than normal); moderate COPD was the average of the mean and the high end of the range (60,75), and severe COPD was the highest value of the range.
- - Dead space:  VD/VT values were taken from Farah et al @cite farah2009can (Table 1). Mild COPD was mean minus 1 standard deviation; moderate COPD was the mean value; severe COPD was mean plus 2 standard deviations. 
- - Shunt: QS/QT values were taken from Torres et al @cite torres1989ventilation (Table 3). Mild COPD was mean minus 2 standard deviations; moderate COPD was the mean value; for severe COPD, values for FiO2 and PaO2 were taken from Arnal et al @cite arnal2018parameters (Table 2) and used with various prediction equations for iso-shunt lines to get a match at about PaO2 = 69, FiO2 = 0.4 and shunt = 0.20 .
- - Ventilator Settings: All ventilator settings were takeng from Arnal et al @cite arnal2018parameters (Table 2) for a male patient aged 73 years and predicted body weight of 60 kg. Note that the mode for simulation is PC-CMV, which is equivalent to the mode used by Arnal et @cite arnal2018parameters for passive pateints. Equivalent settings for tidal volume, rate, and inspiratory time can be used for volume control simulations.
- - Blood Gas Values: Expected blood gas value for outputs of Pulse simulator were taken from the most complete source: Arnal et al @cite arnal2018parameters (Table 2). Expected values for SpO2 were calculated from PaO2 using the equation from Gadrey et al @cite gadrey2019imputation.</t>
-  </si>
-  <si>
-    <t>Configuration</t>
-  </si>
-  <si>
-    <t>{v} = 10</t>
-  </si>
-  <si>
-    <t>{v} = 54</t>
-  </si>
-  <si>
-    <t>{v} &lt; 0.05</t>
-  </si>
-  <si>
-    <t>{v} = 444</t>
-  </si>
-  <si>
-    <t>{v} &gt; 75</t>
-  </si>
-  <si>
-    <t>{v} &lt; 45</t>
-  </si>
-  <si>
-    <t>{v} &gt; 0.95</t>
-  </si>
-  <si>
-    <t>{v} &gt; 300</t>
-  </si>
-  <si>
-    <t>Comparison Formula</t>
-  </si>
-  <si>
-    <t>Threshold</t>
-  </si>
-  <si>
-    <t>{v} = 12</t>
-  </si>
-  <si>
-    <t>{v} = 40</t>
-  </si>
-  <si>
-    <t>{v} = 0.54</t>
-  </si>
-  <si>
-    <t>{v} = 0.2</t>
-  </si>
-  <si>
-    <t>{v} = 414</t>
-  </si>
-  <si>
-    <t>{v} = 35</t>
-  </si>
-  <si>
-    <t>{v} = 0.57</t>
-  </si>
-  <si>
-    <t>{v} = 0.3</t>
-  </si>
-  <si>
-    <t>{v} = 396</t>
-  </si>
-  <si>
-    <t>{v} = 33</t>
-  </si>
-  <si>
-    <t>{v} = 0.65</t>
-  </si>
-  <si>
-    <t>{v} = 0.4</t>
-  </si>
-  <si>
-    <t>{v} &lt; 100</t>
-  </si>
-  <si>
-    <t>{v} = 24</t>
-  </si>
-  <si>
-    <t>{v} = 36</t>
-  </si>
-  <si>
-    <t>{v} = 68</t>
-  </si>
-  <si>
-    <t>{v} = 0.49</t>
-  </si>
-  <si>
-    <t>{v} = 0.19</t>
-  </si>
-  <si>
-    <t>{v} = 534</t>
-  </si>
-  <si>
-    <t>{v} = 34</t>
-  </si>
-  <si>
-    <t>{v} = 51</t>
-  </si>
-  <si>
-    <t>{v} = 75</t>
-  </si>
-  <si>
-    <t>{v} = 0.73</t>
-  </si>
-  <si>
-    <t>{v} = 600</t>
-  </si>
-  <si>
-    <t>{v} = 520</t>
-  </si>
-  <si>
-    <t>{v} = {1}</t>
-  </si>
-  <si>
-    <t>{v} = 18</t>
-  </si>
-  <si>
-    <t>{v} = 60</t>
-  </si>
-  <si>
-    <t>{v} = 0.37</t>
-  </si>
-  <si>
-    <t>{v} = 0.12</t>
-  </si>
-  <si>
-    <t>{v} = 438</t>
-  </si>
-  <si>
-    <t>PhysiologicDeadSpaceTidalVolumeRatio</t>
-  </si>
-  <si>
-    <t>VD/VT (determined from blood gas values)</t>
-  </si>
-  <si>
-    <t>QS/QT (determined from blood gas values)</t>
-  </si>
-  <si>
-    <t>QS/QT (determined from blood gas values) (0.33 +/- 0.15)</t>
-  </si>
-  <si>
-    <t>QS/QT (determined from blood gas values) (0.22 +/- 0.14)</t>
-  </si>
-  <si>
-    <t>Good:0, Fair:1</t>
-  </si>
-  <si>
-    <t>ClinicalShuntFraction</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.5 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.5 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{v} &gt; {1}</t>
-  </si>
-  <si>
-    <t>{v} &lt; {1}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "ContinuousMandatoryVentilation", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.87, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 22, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 23, "Unit": "1/min" } }
+  "RespirationRate": { "ScalarFrequency": { "Value": 17, "Unit": "1/min" } }
   }}
 }</t>
   </si>
@@ -1045,17 +1045,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1078,11 +1072,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1491,50 +1491,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="177.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -1546,11 +1546,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -1569,74 +1569,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="17"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1648,13 +1648,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1664,13 +1664,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
     </row>
@@ -1678,13 +1678,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="B13" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9" t="s">
         <v>100</v>
       </c>
@@ -1694,13 +1694,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1715,13 +1715,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>6</v>
@@ -1741,7 +1741,7 @@
         <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>74</v>
@@ -1763,7 +1763,7 @@
         <v>34</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -1785,7 +1785,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>75</v>
@@ -1801,16 +1801,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="12" t="s">
@@ -1823,20 +1823,20 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -1851,14 +1851,14 @@
         <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -1873,13 +1873,13 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>41</v>
@@ -1897,10 +1897,10 @@
         <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
@@ -1919,10 +1919,10 @@
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="2" t="s">
@@ -1941,10 +1941,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
@@ -1963,10 +1963,10 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="2" t="s">
@@ -1985,10 +1985,10 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="2" t="s">
@@ -1998,6 +1998,19 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
@@ -2005,19 +2018,6 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2047,50 +2047,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="241.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -2102,11 +2102,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -2125,74 +2125,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="17"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -2218,13 +2218,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
         <v>56</v>
       </c>
@@ -2234,13 +2234,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -2250,13 +2250,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -2264,13 +2264,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="B15" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
         <v>101</v>
       </c>
@@ -2280,13 +2280,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -2301,13 +2301,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -2327,7 +2327,7 @@
         <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>74</v>
@@ -2349,7 +2349,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>74</v>
@@ -2371,7 +2371,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>75</v>
@@ -2387,20 +2387,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>75</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -2409,20 +2409,20 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -2437,14 +2437,14 @@
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H23" s="16"/>
     </row>
@@ -2465,7 +2465,7 @@
         <v>74</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -2571,10 +2571,10 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="2" t="s">
@@ -2586,13 +2586,13 @@
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
@@ -2604,13 +2604,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
       <c r="G31" s="9" t="s">
         <v>55</v>
       </c>
@@ -2620,13 +2620,13 @@
       <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B32" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
+      <c r="B32" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
       <c r="G32" s="9" t="s">
         <v>102</v>
       </c>
@@ -2636,13 +2636,13 @@
       <c r="A33" s="8">
         <v>2</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
     </row>
@@ -2657,13 +2657,13 @@
         <v>11</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>6</v>
@@ -2683,7 +2683,7 @@
         <v>34</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>74</v>
@@ -2705,7 +2705,7 @@
         <v>34</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>74</v>
@@ -2727,7 +2727,7 @@
         <v>33</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>75</v>
@@ -2743,20 +2743,20 @@
         <v>23</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>75</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="12" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -2765,20 +2765,20 @@
         <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H39" s="16"/>
     </row>
@@ -2793,14 +2793,14 @@
         <v>36</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H40" s="16"/>
     </row>
@@ -2821,7 +2821,7 @@
         <v>74</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>41</v>
@@ -2927,10 +2927,10 @@
         <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="2" t="s">
@@ -2942,13 +2942,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2960,13 +2960,13 @@
       <c r="A48" s="8">
         <v>3</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
       <c r="G48" s="9" t="s">
         <v>68</v>
       </c>
@@ -2976,13 +2976,13 @@
       <c r="A49" s="8">
         <v>3</v>
       </c>
-      <c r="B49" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
+      <c r="B49" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
       <c r="G49" s="9" t="s">
         <v>103</v>
       </c>
@@ -2992,13 +2992,13 @@
       <c r="A50" s="8">
         <v>3</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
@@ -3013,13 +3013,13 @@
         <v>11</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>6</v>
@@ -3039,7 +3039,7 @@
         <v>34</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>74</v>
@@ -3061,7 +3061,7 @@
         <v>34</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>74</v>
@@ -3083,7 +3083,7 @@
         <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>75</v>
@@ -3099,13 +3099,13 @@
         <v>23</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>75</v>
@@ -3121,20 +3121,20 @@
         <v>23</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H56" s="16"/>
     </row>
@@ -3149,14 +3149,14 @@
         <v>36</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H57" s="16"/>
     </row>
@@ -3177,7 +3177,7 @@
         <v>74</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>41</v>
@@ -3283,10 +3283,10 @@
         <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F63" s="10"/>
       <c r="G63" s="2" t="s">
@@ -3296,15 +3296,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -3320,12 +3317,15 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B47:F47"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3354,50 +3354,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="283.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="F2" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -3409,11 +3409,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3432,74 +3432,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="17"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3511,13 +3511,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
@@ -3525,13 +3525,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
         <v>57</v>
       </c>
@@ -3541,13 +3541,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -3557,13 +3557,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -3571,15 +3571,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="B15" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -3587,13 +3587,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -3608,13 +3608,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -3634,7 +3634,7 @@
         <v>34</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>78</v>
@@ -3656,7 +3656,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>77</v>
@@ -3678,7 +3678,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>74</v>
@@ -3694,20 +3694,20 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="12" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H21" s="16"/>
     </row>
@@ -3716,20 +3716,20 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>80</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H22" s="16"/>
     </row>
@@ -3744,14 +3744,14 @@
         <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H23" s="16"/>
     </row>
@@ -3772,7 +3772,7 @@
         <v>74</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>41</v>
@@ -3849,13 +3849,13 @@
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="1" t="s">
         <v>6</v>
       </c>
@@ -3867,13 +3867,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
       <c r="G29" s="9" t="s">
         <v>69</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
@@ -3899,13 +3899,13 @@
       <c r="A31" s="8">
         <v>2</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
     </row>
@@ -3920,13 +3920,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>6</v>
@@ -3946,7 +3946,7 @@
         <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>78</v>
@@ -3968,7 +3968,7 @@
         <v>34</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>77</v>
@@ -3990,7 +3990,7 @@
         <v>33</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>74</v>
@@ -4006,20 +4006,20 @@
         <v>23</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>79</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="12" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H36" s="16"/>
     </row>
@@ -4028,20 +4028,20 @@
         <v>23</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>80</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H37" s="16"/>
     </row>
@@ -4056,14 +4056,14 @@
         <v>36</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H38" s="16"/>
     </row>
@@ -4084,7 +4084,7 @@
         <v>74</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>41</v>
@@ -4161,13 +4161,13 @@
       <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
       <c r="G43" s="1" t="s">
         <v>6</v>
       </c>
@@ -4179,13 +4179,13 @@
       <c r="A44" s="8">
         <v>3</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
       <c r="G44" s="9" t="s">
         <v>70</v>
       </c>
@@ -4196,14 +4196,14 @@
         <v>3</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
       <c r="E45" s="31"/>
       <c r="F45" s="32"/>
       <c r="G45" s="9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H45" s="9"/>
     </row>
@@ -4211,13 +4211,13 @@
       <c r="A46" s="8">
         <v>3</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
@@ -4232,13 +4232,13 @@
         <v>11</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>6</v>
@@ -4258,7 +4258,7 @@
         <v>34</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>78</v>
@@ -4280,7 +4280,7 @@
         <v>34</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>77</v>
@@ -4302,7 +4302,7 @@
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>74</v>
@@ -4318,13 +4318,13 @@
         <v>23</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>79</v>
@@ -4340,20 +4340,20 @@
         <v>23</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H52" s="16"/>
     </row>
@@ -4368,14 +4368,14 @@
         <v>36</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>74</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H53" s="16"/>
     </row>
@@ -4396,7 +4396,7 @@
         <v>74</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>41</v>
@@ -4471,15 +4471,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
@@ -4495,12 +4492,15 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="G6:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4529,50 +4529,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17"/>
+      <c r="D1" s="26"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
@@ -4584,11 +4584,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -4607,74 +4607,74 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="17"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4700,15 +4700,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="B12" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="G12" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -4716,13 +4716,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -4732,13 +4732,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -4746,13 +4746,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="B15" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9" t="s">
         <v>105</v>
       </c>
@@ -4762,13 +4762,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -4783,13 +4783,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>6</v>
@@ -4809,14 +4809,14 @@
         <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H18" s="16"/>
     </row>
@@ -4847,7 +4847,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H20" s="16"/>
     </row>
@@ -4868,13 +4868,13 @@
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
@@ -4886,15 +4886,15 @@
       <c r="A22" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
+      <c r="B22" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
       <c r="G22" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H22" s="9"/>
     </row>
@@ -4902,13 +4902,13 @@
       <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
     </row>
@@ -4923,13 +4923,13 @@
         <v>11</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>6</v>
@@ -4949,14 +4949,14 @@
         <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H25" s="16"/>
     </row>
@@ -4971,7 +4971,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>62</v>
@@ -4993,7 +4993,7 @@
         <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>61</v>
@@ -5037,7 +5037,7 @@
         <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>61</v>
@@ -5053,7 +5053,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>25</v>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H30" s="16"/>
     </row>
@@ -5075,25 +5075,41 @@
         <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>61</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H31" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G6:H9"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
@@ -5103,22 +5119,6 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G6:H9"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
